--- a/registration_forms/033_placement_registration_form--registration_forms.xlsx
+++ b/registration_forms/033_placement_registration_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1079,8 +1079,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'denied'}</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'denied'}</t>
+          <t>denied</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'seeking_employment'}</t>
+          <t>seeking_employment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'seeking_employment'}</t>
+          <t>seeking employment</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'self_employed'}</t>
+          <t>self_employed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'self_employed'}</t>
+          <t>self employed</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'full_time'}</t>
+          <t>full_time</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'full_time'}</t>
+          <t>full time</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'part_time'}</t>
+          <t>part_time</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'part_time'}</t>
+          <t>part time</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'freelance'}</t>
+          <t>freelance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'freelance'}</t>
+          <t>freelance</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'software_development'}</t>
+          <t>software_development</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'software_development'}</t>
+          <t>software development</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'customer_service'}</t>
+          <t>customer_service</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'customer_service'}</t>
+          <t>customer service</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'finance'}</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'finance'}</t>
+          <t>finance</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'design'}</t>
+          <t>design</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'design'}</t>
+          <t>design</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'human_resources'}</t>
+          <t>human_resources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'human_resources'}</t>
+          <t>human resources</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'active'}</t>
+          <t>active</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'deleted'}</t>
+          <t>deleted</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'deleted'}</t>
+          <t>deleted</t>
         </is>
       </c>
     </row>
